--- a/dados/excel/quadro_tempo_servico.xlsx
+++ b/dados/excel/quadro_tempo_servico.xlsx
@@ -7,18 +7,22 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dados" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Metadados" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Metadados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dados" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$E$8</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;R$&quot; #,##0.00"/>
+  </numFmts>
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,14 +32,37 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="000D2B4E"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="004A5568"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="004A5568"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="001A1A1A"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -44,12 +71,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00003A70"/>
-        <bgColor rgb="00003A70"/>
+        <fgColor rgb="000D2B4E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F7FA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -58,25 +89,60 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color rgb="004A90D9"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D8DEE6"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D8DEE6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D8DEE6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D8DEE6"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -443,233 +509,242 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TEMPO DE CASA</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>REGISTROS</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>MATRÍCULAS ÚNICAS</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>FOLHA BRUTA (R$)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>FOLHA MÉDIA (R$)</t>
+          <t>Tempo de casa (contagem)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>0-5</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>177749</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>7437</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>880328212.48</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>4952.647905079635</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>6-10</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>104833</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>2523</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>575151029.03</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>5486.354764530252</t>
+          <t>Fonte: Portal da Transparência de Sorocaba · Organizado pelo Observatório Social do Brasil — Sorocaba · Licença CC-BY 4.0</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>11-15</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>226806</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>4412</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1544541576.93</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6809.9678885479225</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>16-20</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>132453</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2339</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1206561251.62</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9109.35389624999</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Para que serve</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Experiência geral.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>21-25</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>52364</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>520666592.59</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>9943.216572263387</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Informações técnicas</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>26-30</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>13130</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>155284525.12</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>11826.69650571211</t>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>quadro_tempo_servico.csv</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>30+</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>143182</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>8836</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>974123315.94</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6803.392297495496</t>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Descrição</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Servidores por faixa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Linhas</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Colunas</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Separador</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>ponto e vírgula</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Codificação</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>utf-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Gerado em</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>24/09/2026 19:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Dicionário de colunas</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Coluna</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Formato no Excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>﻿faixa_tempo</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Número decimal (#,##0,00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>num_registros</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Número decimal (#,##0,00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>num_matriculas</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Número decimal (#,##0,00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>folha_total</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>moeda</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Moeda (R$ #,##0,00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>folha_media</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>moeda</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Moeda (R$ #,##0,00)</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -680,86 +755,178 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CAMPO</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>VALOR</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>﻿faixa_tempo</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>num_registros</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>num_matriculas</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>folha_total</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>folha_media</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>FONTE</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Portal da Transparência de Sorocaba</t>
-        </is>
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="n">
+        <v>177749</v>
+      </c>
+      <c r="C2" s="9" t="n">
+        <v>7437</v>
+      </c>
+      <c r="D2" s="10" t="n">
+        <v>880328212.48</v>
+      </c>
+      <c r="E2" s="10" t="n">
+        <v>4952.647905079635</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>https://transparencia.sorocaba.sp.gov.br</t>
-        </is>
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>6-10</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="n">
+        <v>104833</v>
+      </c>
+      <c r="C3" s="12" t="n">
+        <v>2523</v>
+      </c>
+      <c r="D3" s="13" t="n">
+        <v>575151029.03</v>
+      </c>
+      <c r="E3" s="13" t="n">
+        <v>5486.354764530252</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>PERÍODO</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>2022-01 a 2026-08</t>
-        </is>
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>11-15</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>226806</v>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>4412</v>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>1544541576.93</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>6809.967888547922</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>LICENÇA</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0 — Observatório Social do Brasil — Sorocaba</t>
-        </is>
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>16-20</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>132453</v>
+      </c>
+      <c r="C5" s="12" t="n">
+        <v>2339</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>1206561251.62</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>9109.35389624999</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>GERADO EM</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23 18:50</t>
-        </is>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>21-25</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>52364</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>1157</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>520666592.59</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>9943.216572263387</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>26-30</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>13130</v>
+      </c>
+      <c r="C7" s="12" t="n">
+        <v>287</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>155284525.12</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>11826.69650571211</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>30+</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>143182</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>8836</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>974123315.9400001</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>6803.392297495496</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/dados/excel/quadro_tempo_servico.xlsx
+++ b/dados/excel/quadro_tempo_servico.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -799,16 +799,16 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>177749</v>
+        <v>183736</v>
       </c>
       <c r="C2" s="9" t="n">
-        <v>7437</v>
+        <v>7852</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>880328212.48</v>
+        <v>914259136.61</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>4952.647905079635</v>
+        <v>4975.939046294684</v>
       </c>
     </row>
     <row r="3">
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>104833</v>
+        <v>107009</v>
       </c>
       <c r="C3" s="12" t="n">
-        <v>2523</v>
+        <v>2740</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>575151029.03</v>
+        <v>591166741.76</v>
       </c>
       <c r="E3" s="13" t="n">
-        <v>5486.354764530252</v>
+        <v>5524.458146137241</v>
       </c>
     </row>
     <row r="4">
@@ -837,16 +837,16 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>226806</v>
+        <v>230314</v>
       </c>
       <c r="C4" s="9" t="n">
-        <v>4412</v>
+        <v>4469</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>1544541576.93</v>
+        <v>1577195561.84</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>6809.967888547922</v>
+        <v>6848.022967948105</v>
       </c>
     </row>
     <row r="5">
@@ -856,16 +856,16 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>132453</v>
+        <v>134485</v>
       </c>
       <c r="C5" s="12" t="n">
-        <v>2339</v>
+        <v>2347</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>1206561251.62</v>
+        <v>1231866449.07</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>9109.35389624999</v>
+        <v>9159.879905342603</v>
       </c>
     </row>
     <row r="6">
@@ -875,16 +875,16 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>52364</v>
+        <v>53171</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>1157</v>
+        <v>1164</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>520666592.59</v>
+        <v>531020191.57</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>9943.216572263387</v>
+        <v>9987.026604163924</v>
       </c>
     </row>
     <row r="7">
@@ -894,16 +894,16 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>13130</v>
+        <v>13327</v>
       </c>
       <c r="C7" s="12" t="n">
         <v>287</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>155284525.12</v>
+        <v>158318562.28</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>11826.69650571211</v>
+        <v>11879.5349501013</v>
       </c>
     </row>
     <row r="8">
@@ -913,16 +913,16 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>143182</v>
+        <v>143730</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>8836</v>
+        <v>8942</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>974123315.9400001</v>
+        <v>982801080.4</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>6803.392297495496</v>
+        <v>6837.828431086064</v>
       </c>
     </row>
   </sheetData>
